--- a/app/public/templates/client-import-template.xlsx
+++ b/app/public/templates/client-import-template.xlsx
@@ -474,13 +474,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Настройки → «Импорт базы» → Шаг 2 «Залить контакты и балансы в CRM» → выберите этот файл (заполненный лист «Клиенты»).</t>
+          <t>Настройки → «Импорт базы» → Шаг 1 «Загрузить и проверить» → скачается проверенный файл → поправьте строки с «Проверить = Да» → загрузите на Шаге 2.</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Из списка (см. ниже)</t>
+          <t>Состояние клиента как в «Контактах» (см. ниже)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Продажа</t>
+          <t>Активный</t>
         </is>
       </c>
     </row>
@@ -741,7 +741,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Название филиала точно как в CRM (иначе импорт отклонится)</t>
+          <t>Название филиала точно как заведено в CRM (иначе импорт отклонится)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Допустимые значения столбца «Статус»</t>
+          <t>Допустимые значения столбца «Статус» (как в разделе «Контакты»)</t>
         </is>
       </c>
       <c r="B24" s="1" t="n"/>
@@ -808,154 +808,130 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Новый лид (в воронке)</t>
+          <t>Новый лид</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Предзапись</t>
+          <t>Потенциал</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Новый лид (предзапись)</t>
+          <t>Потенциальный клиент</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Пробник</t>
+          <t>Нецелевой</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Записан на пробное занятие</t>
+          <t>Нецелевой лид</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Потенциал</t>
+          <t>Активный</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Потенциальный клиент</t>
+          <t>Активный (платящий) клиент</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Нецелевой</t>
+          <t>Выбывший</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Нецелевой лид</t>
+          <t>Бывший клиент (отток)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Продажа</t>
+          <t>Архив</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Активный (платящий) клиент</t>
+          <t>Архив</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Выбыл</t>
+          <t>Чёрный список</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Бывший клиент (отток)</t>
+          <t>Чёрный список</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Архив</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Архив</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Черный список</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Чёрный список</t>
-        </is>
-      </c>
-    </row>
+          <t>Синонимы тоже понимаются: «Продажа» = Активный, «Выбыл»/«Выбывшие» = Выбывший, «ЧС» = Чёрный список.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Синонимы тоже понимаются: «ЧС» = Черный список, «Выбывший/Выбывшие» = Выбыл.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>Важно:</t>
+        </is>
+      </c>
+      <c r="B35" s="1" t="n"/>
+      <c r="C35" s="1" t="n"/>
+      <c r="D35" s="1" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>•  Заголовки в строке 1 листа «Клиенты» не переименовывайте — по ним CRM находит колонки.</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>Важно:</t>
-        </is>
-      </c>
-      <c r="B37" s="1" t="n"/>
-      <c r="C37" s="1" t="n"/>
-      <c r="D37" s="1" t="n"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>•  Не загружайте лист «Инструкция» — импортируется только лист «Клиенты».</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>•  Заголовки в строке 1 листа «Клиенты» не переименовывайте — по ним CRM находит колонки.</t>
+          <t>•  Телефоны пишите единообразно: +7… и 8… считаются разными номерами (клиент может задвоиться).</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>•  Не загружайте лист «Инструкция» — импортируется только лист «Клиенты».</t>
+          <t>•  Если у клиента несколько детей — по строке на каждого ребёнка, телефон один и тот же.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
-        <is>
-          <t>•  Телефоны пишите единообразно: +7… и 8… считаются разными номерами (клиент может задвоиться).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>•  Если у клиента несколько детей — по строке на каждого ребёнка, телефон один и тот же.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
         <is>
           <t>•  Филиал должен уже существовать в CRM с точно таким же названием, иначе весь файл не загрузится.</t>
         </is>
